--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -62796,7 +62796,7 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
         <v>0</v>
@@ -62819,7 +62819,7 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
         <v>0</v>
@@ -62842,7 +62842,7 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
         <v>0</v>
@@ -62865,7 +62865,7 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
         <v>0</v>
@@ -62888,7 +62888,7 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
         <v>0</v>
@@ -62911,7 +62911,7 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
         <v>0</v>
@@ -62929,6 +62929,29 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>
